--- a/data/dividends_info_20260917.xlsx
+++ b/data/dividends_info_20260917.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>42.65499877929688</v>
+        <v>42.43999862670898</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2109952000366311</v>
+        <v>0.2120640973427361</v>
       </c>
       <c r="J2" t="n">
         <v>179</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.40000152587891</v>
+        <v>66</v>
       </c>
       <c r="I3" t="n">
-        <v>1.070336366464775</v>
+        <v>1.060606060606061</v>
       </c>
       <c r="J3" t="n">
         <v>158</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.859999656677246</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6772009291759016</v>
+        <v>0.6622516249567504</v>
       </c>
       <c r="J4" t="n">
         <v>88</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.4900000095367432</v>
       </c>
       <c r="I5" t="n">
-        <v>0.784313740156468</v>
+        <v>0.8163265147242933</v>
       </c>
       <c r="J5" t="n">
         <v>88</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42.65499877929688</v>
+        <v>42.43999862670898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2109952000366311</v>
+        <v>0.2120640973427361</v>
       </c>
       <c r="J6" t="n">
         <v>88</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.095000028610229</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I7" t="n">
-        <v>3.675417610904753</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J7" t="n">
         <v>67</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.97500038146973</v>
+        <v>24.09000015258789</v>
       </c>
       <c r="I8" t="n">
-        <v>1.126173079057312</v>
+        <v>1.120797004108757</v>
       </c>
       <c r="J8" t="n">
         <v>67</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.59000015258789</v>
+        <v>24.51000022888184</v>
       </c>
       <c r="I9" t="n">
-        <v>2.399349314106887</v>
+        <v>2.407180720075074</v>
       </c>
       <c r="J9" t="n">
         <v>67</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.079999923706055</v>
+        <v>6.019999980926514</v>
       </c>
       <c r="I10" t="n">
-        <v>3.289473725487982</v>
+        <v>3.322259146738715</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.77000045776367</v>
+        <v>10.73999977111816</v>
       </c>
       <c r="I11" t="n">
-        <v>4.271123309641125</v>
+        <v>4.283054095001237</v>
       </c>
       <c r="J11" t="n">
         <v>39</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.849999904632568</v>
+        <v>8.050000190734863</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7643312194767268</v>
+        <v>0.7453415972468785</v>
       </c>
       <c r="J12" t="n">
         <v>32</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.4900000095367432</v>
       </c>
       <c r="I13" t="n">
-        <v>0.784313740156468</v>
+        <v>0.8163265147242933</v>
       </c>
       <c r="J13" t="n">
         <v>32</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.599999904632568</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8928571580624097</v>
+        <v>0.8865248436815314</v>
       </c>
       <c r="J14" t="n">
         <v>18</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6.980000019073486</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5444126059621996</v>
+        <v>0.5277777917591145</v>
       </c>
       <c r="J15" t="n">
         <v>11</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.97500038146973</v>
+        <v>24.09000015258789</v>
       </c>
       <c r="I16" t="n">
-        <v>1.126173079057312</v>
+        <v>1.120797004108757</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.955999970436096</v>
+        <v>1.978000044822693</v>
       </c>
       <c r="I17" t="n">
-        <v>2.914110473493089</v>
+        <v>2.881698620239893</v>
       </c>
       <c r="J17" t="n">
         <v>4</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>42.65499877929688</v>
+        <v>42.43999862670898</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2109952000366311</v>
+        <v>0.2120640973427361</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>96.90000152587891</v>
+        <v>98.59999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>1.372548997994391</v>
+        <v>1.348884402213329</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.239999771118164</v>
+        <v>6.28000020980835</v>
       </c>
       <c r="I20" t="n">
-        <v>4.807692484037417</v>
+        <v>4.777069904097268</v>
       </c>
       <c r="J20" t="n">
         <v>-3</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.4900000095367432</v>
       </c>
       <c r="I21" t="n">
-        <v>0.784313740156468</v>
+        <v>0.8163265147242933</v>
       </c>
       <c r="J21" t="n">
         <v>-24</v>
@@ -2686,7 +2686,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2703,7 +2703,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2720,7 +2720,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2737,7 +2737,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2771,7 +2771,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3002,14 +3002,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3043,7 +3043,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3053,14 +3053,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3087,14 +3087,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3104,14 +3104,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3128,7 +3128,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3145,7 +3145,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3155,14 +3155,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3179,7 +3179,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3189,14 +3189,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3206,14 +3206,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3230,7 +3230,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3247,7 +3247,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3264,7 +3264,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3281,7 +3281,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3298,7 +3298,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3308,14 +3308,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3325,14 +3325,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Guidotti Ships S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3383,7 +3383,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3400,7 +3400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3434,7 +3434,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3451,7 +3451,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3461,14 +3461,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3485,7 +3485,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3519,7 +3519,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3536,7 +3536,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3570,7 +3570,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3587,7 +3587,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3604,7 +3604,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3621,7 +3621,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3655,7 +3655,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3672,7 +3672,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3689,7 +3689,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3706,7 +3706,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3740,7 +3740,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3750,14 +3750,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3774,7 +3774,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3791,7 +3791,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3808,7 +3808,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3835,14 +3835,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3859,7 +3859,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3876,7 +3876,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3893,7 +3893,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3927,7 +3927,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3978,7 +3978,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3995,7 +3995,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4012,7 +4012,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4029,7 +4029,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4046,7 +4046,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4080,7 +4080,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4090,14 +4090,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4114,7 +4114,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4131,7 +4131,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4165,7 +4165,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4199,7 +4199,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4216,7 +4216,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4250,7 +4250,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4267,7 +4267,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4284,7 +4284,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4335,7 +4335,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4369,7 +4369,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4386,7 +4386,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4420,7 +4420,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4488,7 +4488,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4505,7 +4505,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4522,7 +4522,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4556,7 +4556,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4573,7 +4573,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4583,14 +4583,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4607,7 +4607,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4624,7 +4624,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4641,7 +4641,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4658,7 +4658,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4668,14 +4668,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4692,7 +4692,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4702,14 +4702,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4760,7 +4760,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4777,7 +4777,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4787,14 +4787,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4828,7 +4828,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4862,7 +4862,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4879,7 +4879,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4913,7 +4913,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4923,14 +4923,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4947,7 +4947,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4964,7 +4964,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4981,7 +4981,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4998,7 +4998,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5015,7 +5015,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5032,7 +5032,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5066,7 +5066,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5083,7 +5083,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5100,7 +5100,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5134,7 +5134,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5168,7 +5168,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5219,7 +5219,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5236,7 +5236,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5253,7 +5253,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5304,7 +5304,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5314,14 +5314,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5338,7 +5338,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5355,7 +5355,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5372,7 +5372,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5406,7 +5406,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5423,7 +5423,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5440,7 +5440,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5457,7 +5457,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5474,7 +5474,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5559,7 +5559,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5569,14 +5569,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5586,14 +5586,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5603,14 +5603,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5620,14 +5620,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5637,14 +5637,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5688,14 +5688,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5705,14 +5705,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5790,14 +5790,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5831,7 +5831,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5848,7 +5848,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5858,14 +5858,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5882,7 +5882,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5892,14 +5892,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5954,78 +5954,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BEEWIZE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DHH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>